--- a/Esoft/AAC_Sprint_Tracker.xlsx
+++ b/Esoft/AAC_Sprint_Tracker.xlsx
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -196,9 +196,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1580,9 +1577,9 @@
           <t>Implement trilingual switching framework (English complete, Sinhala/Tamil partial)</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1595,9 +1592,9 @@
           <t>Integrate basic text-to-speech (English functional, Sinhala/Tamil under evaluation)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1739,9 +1736,9 @@
           <t>Finalise symbol set and resolve licensing</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1754,9 +1751,9 @@
           <t>Complete Sinhala and Tamil vocabulary</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1769,9 +1766,9 @@
           <t>Evaluate alternative TTS engines for Sinhala/Tamil</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1784,9 +1781,9 @@
           <t>Complete curated dataset (2,000-5,000 images)</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1799,9 +1796,9 @@
           <t>Full model training with hyperparameter tuning</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1814,9 +1811,9 @@
           <t>TFLite export and on-device benchmarking</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1829,9 +1826,9 @@
           <t>Submit ethics application</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>In Preparation</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1868,9 +1865,9 @@
           <t>Integrate FER pipeline into Flutter application</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1883,9 +1880,9 @@
           <t>Implement emotion-adaptive logic and caregiver override</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1898,9 +1895,9 @@
           <t>Complete therapist-parent dashboard</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1913,9 +1910,9 @@
           <t>Follow up on ethics approval</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1928,9 +1925,9 @@
           <t>Design pilot protocol and recruit participants</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1967,9 +1964,9 @@
           <t>Conduct supervised pilot at Karapitiya Teaching Hospital</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -2027,9 +2024,9 @@
           <t>Prepare and deliver final presentation</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2140,16 +2137,13 @@
       </c>
       <c r="B6" s="13" t="inlineStr"/>
       <c r="C6" s="13" t="inlineStr"/>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Trilingual switching
-Sinhala/Tamil TTS</t>
-        </is>
-      </c>
+      <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Symbol grid UI
+Trilingual switching
+Sinhala/Tamil TTS
 Local data layer
 Firebase setup
 AI pipeline setup
@@ -2167,27 +2161,24 @@
 Mar 26</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Sinhala/Tamil vocab
-TTS evaluation
+      <c r="B7" s="13" t="inlineStr"/>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>TTS evaluation
+TFLite export</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Symbol set licensing
+Sinhala/Tamil vocab
 Dataset curation
 Model training
-TFLite export</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Ethics application</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Symbol set licensing</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
+Ethics application</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -2196,19 +2187,22 @@
 Apr 26</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr"/>
+      <c r="C8" s="13" t="inlineStr"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Emotion-adaptive logic
+Pilot protocol</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>FER integration
-Emotion-adaptive logic
 Dashboard
-Ethics follow-up
-Pilot protocol</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-      <c r="D8" s="13" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
+Ethics follow-up</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -2217,46 +2211,52 @@
 May 26</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Pilot execution
-Data collection
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Data collection
 Analysis
-Final report
-Presentation</t>
+Final report</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr"/>
-      <c r="D9" s="13" t="inlineStr"/>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Pilot execution</t>
+        </is>
+      </c>
       <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr"/>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr"/>
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr"/>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr"/>
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Pending / Backlog</t>
         </is>
@@ -2377,17 +2377,17 @@
         <v>10</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>80%</t>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2406,17 +2406,17 @@
         <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>71%</t>
         </is>
       </c>
     </row>
@@ -2435,17 +2435,17 @@
         <v>5</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
     </row>
@@ -2464,24 +2464,24 @@
         <v>5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Overall Progress: 14 of 33 tasks completed (42%). Sprint 3 in progress (as of 25 March 2026). Project deadline: May 2026.</t>
+          <t>Overall Progress: 25 of 33 tasks completed (76%). Platform B integration and pilot-readiness activities are in progress. Project deadline: May 2026.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
           <t>Flutter iOS build target requires macOS for testing</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3543,7 +3543,7 @@
           <t>Sinhala TTS output quality poor with default Flutter TTS engine</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3580,7 +3580,7 @@
           <t>Tamil TTS not functional on all Android devices</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3617,7 +3617,7 @@
           <t>Google Colab free tier session timeout during training</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3654,7 +3654,7 @@
           <t>Colab session lost unsaved training progress</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3691,7 +3691,7 @@
           <t>Western-centric AAC symbol sets not suitable for Sri Lankan context</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3728,7 +3728,7 @@
           <t>Symbol set licensing terms unclear for open-source redistribution</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3765,7 +3765,7 @@
           <t>Test accuracy (66%) significantly lower than validation accuracy (82-84%)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3802,7 +3802,7 @@
           <t>Default widget_test.dart fails due to MyApp constructor mismatch</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3839,7 +3839,7 @@
           <t>Apple Developer account not available for iOS deployment</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4221,7 +4221,7 @@
       </c>
     </row>
     <row r="4" ht="100" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Sprint 1
 (Nov-Dec 2025)</t>
@@ -4251,7 +4251,7 @@
       </c>
     </row>
     <row r="5" ht="100" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Sprint 2
 (Jan-Feb 2026)</t>
@@ -4284,7 +4284,7 @@
       </c>
     </row>
     <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Sprint 3
 (Mar 2026)
